--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_biobio.xlsx
@@ -120,18 +120,18 @@
     <t xml:space="preserve">Antuco</t>
   </si>
   <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1050,7 +1050,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8205</v>
+        <v>8201</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1063,7 +1063,7 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>8201</v>
+        <v>8314</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -1089,7 +1089,7 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8314</v>
+        <v>8205</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:19</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
